--- a/SCH-STH/Impact assessments/Senegal/2025/november/sn_sppa_impact_2511_2_child.xlsx
+++ b/SCH-STH/Impact assessments/Senegal/2025/november/sn_sppa_impact_2511_2_child.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\SCH-STH\Impact assessments\Senegal\2025\november\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DB71AB0-838A-4B1A-BC5A-4CC3D40179C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C64B18B-AEA6-426B-9FF8-ABA02C5F412B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>

--- a/SCH-STH/Impact assessments/Senegal/2025/november/sn_sppa_impact_2511_2_child.xlsx
+++ b/SCH-STH/Impact assessments/Senegal/2025/november/sn_sppa_impact_2511_2_child.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\SCH-STH\Impact assessments\Senegal\2025\november\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C64B18B-AEA6-426B-9FF8-ABA02C5F412B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A22DF89-8611-422D-904A-839C0D236083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -168,27 +168,15 @@
     <t>Dans.les.toilettes.de.l.ecole</t>
   </si>
   <si>
-    <t>Dans les toilettes de l'école</t>
-  </si>
-  <si>
     <t>Autour.de.la.cloture.de.l.ecole</t>
   </si>
   <si>
-    <t>Autour de la cloture de l'école</t>
-  </si>
-  <si>
     <t>a.l.exterieur.de.l.ecole</t>
   </si>
   <si>
-    <t>À l'extérieur de l'école</t>
-  </si>
-  <si>
     <t>J.attends/Je.me.retiens</t>
   </si>
   <si>
-    <t>J'attends/Je me retiens</t>
-  </si>
-  <si>
     <t>Ne.sais.pas</t>
   </si>
   <si>
@@ -219,15 +207,9 @@
     <t>Eau.non.disponible.a.l.ecole</t>
   </si>
   <si>
-    <t>Eau non disponible à l'école</t>
-  </si>
-  <si>
     <t>J.oublie.toujours</t>
   </si>
   <si>
-    <t>J'oublie toujours</t>
-  </si>
-  <si>
     <t>Je.ne.pense.pas.que.ce.soit.important</t>
   </si>
   <si>
@@ -255,15 +237,9 @@
     <t>Traversee.de.cours.d.eau</t>
   </si>
   <si>
-    <t>Traversée de cours d'eau</t>
-  </si>
-  <si>
     <t>Puisage.de.l.eau.dans.des.cours.d.eau</t>
   </si>
   <si>
-    <t>Puisage de l'eau dans des cours d'eau</t>
-  </si>
-  <si>
     <t>Jouer</t>
   </si>
   <si>
@@ -435,9 +411,6 @@
     <t>Excellent (très propre, inodore, présence de porte, toit et disponibilité d eau)</t>
   </si>
   <si>
-    <t>Excellent (très propre, inodore, présence de porte, toit et disponibilité d'eau)</t>
-  </si>
-  <si>
     <t>toilet_type</t>
   </si>
   <si>
@@ -499,9 +472,6 @@
   </si>
   <si>
     <t>Au bord des eaux de surface (rivière, marre, fleuve...)</t>
-  </si>
-  <si>
-    <t>Dans les maisons d'à côté</t>
   </si>
   <si>
     <t>select_multiple manif_bilh_list</t>
@@ -711,9 +681,6 @@
     <t>QRManual</t>
   </si>
   <si>
-    <t>Scannez le QR/code-barres avec l'appareil</t>
-  </si>
-  <si>
     <t>Saisie manuelle (en cas de panne du scanner)</t>
   </si>
   <si>
@@ -757,9 +724,6 @@
   </si>
   <si>
     <t>Compris</t>
-  </si>
-  <si>
-    <t>J'ai lu et compris</t>
   </si>
   <si>
     <t>concat(${p_site_code}, '-', ${p_index_init} + position(..))</t>
@@ -855,9 +819,6 @@
     <t>En avalant des œufs ou des larves de vers sans le savoir.</t>
   </si>
   <si>
-    <t>En buvant de l’eau sale ou en mangeant des aliments sales.</t>
-  </si>
-  <si>
     <t>En touchant des surfaces ou des objets sales.</t>
   </si>
   <si>
@@ -870,9 +831,6 @@
     <t>En.avalant.des.œufs.ou.des.larves.de.vers.sans.le.savoir.</t>
   </si>
   <si>
-    <t>En.buvant.de.l’eau.sale.ou.en.mangeant.des.aliments.sales.</t>
-  </si>
-  <si>
     <t>En.touchant.des.surfaces.ou.des.objets.sales.</t>
   </si>
   <si>
@@ -922,6 +880,48 @@
   </si>
   <si>
     <t>select_multiple prevSth</t>
+  </si>
+  <si>
+    <t>Dans les toilettes de l.école</t>
+  </si>
+  <si>
+    <t>Autour de la cloture de l.école</t>
+  </si>
+  <si>
+    <t>À l.extérieur de l.école</t>
+  </si>
+  <si>
+    <t>J.attends/Je me retiens</t>
+  </si>
+  <si>
+    <t>Eau non disponible à l.école</t>
+  </si>
+  <si>
+    <t>J.oublie toujours</t>
+  </si>
+  <si>
+    <t>Traversée de cours d.eau</t>
+  </si>
+  <si>
+    <t>Puisage de l.eau dans des cours d.eau</t>
+  </si>
+  <si>
+    <t>Excellent (très propre, inodore, présence de porte, toit et disponibilité d.eau)</t>
+  </si>
+  <si>
+    <t>Dans les maisons d.à côté</t>
+  </si>
+  <si>
+    <t>Scannez le QR/code-barres avec l.appareil</t>
+  </si>
+  <si>
+    <t>J.ai lu et compris</t>
+  </si>
+  <si>
+    <t>En.buvant.de.l.eau.sale.ou.en.mangeant.des.aliments.sales.</t>
+  </si>
+  <si>
+    <t>En buvant de l.eau sale ou en mangeant des aliments sales.</t>
   </si>
 </sst>
 </file>
@@ -1672,34 +1672,34 @@
         <v>11</v>
       </c>
       <c r="M1" s="36" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="N1" s="36" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="O1" s="36" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="P1" s="36" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="Q1" s="36" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="R1" s="37" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="S1" s="37" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="T1" s="36" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="U1" s="36" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="V1" s="36" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1710,17 +1710,17 @@
         <v>12</v>
       </c>
       <c r="C2" s="40" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="D2" s="41" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E2" s="42"/>
       <c r="F2" s="42" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="G2" s="41" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
@@ -1744,10 +1744,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="C3" s="43" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D3" s="41"/>
       <c r="E3" s="42"/>
@@ -1761,7 +1761,7 @@
       <c r="M3" s="42"/>
       <c r="N3" s="42"/>
       <c r="O3" s="42" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="P3" s="42"/>
       <c r="Q3" s="42"/>
@@ -1778,7 +1778,7 @@
         <v>15</v>
       </c>
       <c r="C4" s="43" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="D4" s="44"/>
       <c r="E4" s="45"/>
@@ -1794,10 +1794,10 @@
       <c r="M4" s="45"/>
       <c r="N4" s="45"/>
       <c r="O4" s="45" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="P4" s="46" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="Q4" s="45"/>
       <c r="R4" s="45"/>
@@ -1810,10 +1810,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="70" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="C5" s="71" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="D5" s="72"/>
       <c r="E5" s="73"/>
@@ -1828,11 +1828,11 @@
       <c r="L5" s="73"/>
       <c r="M5" s="73"/>
       <c r="O5" s="45" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="P5" s="45"/>
       <c r="Q5" s="46" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:22" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -1843,7 +1843,7 @@
         <v>16</v>
       </c>
       <c r="C6" s="43" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="D6" s="44"/>
       <c r="E6" s="45"/>
@@ -1859,11 +1859,11 @@
       <c r="M6" s="45"/>
       <c r="N6" s="45"/>
       <c r="O6" s="45" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="P6" s="45"/>
       <c r="Q6" s="46" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="R6" s="45"/>
       <c r="S6" s="45"/>
@@ -1878,7 +1878,7 @@
         <v>17</v>
       </c>
       <c r="C7" s="43" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="D7" s="44"/>
       <c r="E7" s="45"/>
@@ -1894,13 +1894,13 @@
       <c r="M7" s="45"/>
       <c r="N7" s="45"/>
       <c r="O7" s="45" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="P7" s="45"/>
       <c r="Q7" s="45"/>
       <c r="R7" s="46"/>
       <c r="S7" s="46" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="T7" s="45"/>
       <c r="U7" s="45"/>
@@ -1910,10 +1910,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C8" s="43" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="D8" s="44"/>
       <c r="E8" s="45"/>
@@ -1929,14 +1929,14 @@
       <c r="M8" s="45"/>
       <c r="N8" s="45"/>
       <c r="O8" s="45" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="P8" s="45"/>
       <c r="Q8" s="45"/>
       <c r="R8" s="45"/>
       <c r="S8" s="46"/>
       <c r="T8" s="46" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="U8" s="45"/>
     </row>
@@ -1948,7 +1948,7 @@
         <v>19</v>
       </c>
       <c r="C9" s="44" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="D9" s="44"/>
       <c r="E9" s="42"/>
@@ -1971,13 +1971,13 @@
     </row>
     <row r="10" spans="1:22" s="28" customFormat="1" ht="126" x14ac:dyDescent="0.25">
       <c r="A10" s="34" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="D10" s="44"/>
       <c r="E10" s="63"/>
@@ -2002,10 +2002,10 @@
     </row>
     <row r="11" spans="1:22" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="65" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="B11" s="65" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="C11" s="65"/>
       <c r="D11" s="65"/>
@@ -2014,7 +2014,7 @@
       <c r="G11" s="65"/>
       <c r="H11" s="65"/>
       <c r="I11" s="65" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="J11" s="65"/>
       <c r="K11" s="65"/>
@@ -2027,10 +2027,10 @@
     </row>
     <row r="12" spans="1:22" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="30" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="C12" s="31"/>
       <c r="D12" s="31"/>
@@ -2039,7 +2039,7 @@
       <c r="G12" s="32"/>
       <c r="H12" s="31"/>
       <c r="I12" s="31" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="J12" s="31"/>
       <c r="K12" s="31"/>
@@ -2058,13 +2058,13 @@
     </row>
     <row r="13" spans="1:22" s="29" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="37" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="B13" s="48" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="48"/>
@@ -2087,10 +2087,10 @@
     </row>
     <row r="14" spans="1:22" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="30" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="C14" s="31"/>
       <c r="D14" s="31"/>
@@ -2099,7 +2099,7 @@
       <c r="G14" s="32"/>
       <c r="H14" s="31"/>
       <c r="I14" s="31" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="J14" s="31"/>
       <c r="K14" s="31"/>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="15" spans="1:22" s="28" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A15" s="30" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="C15" s="31"/>
       <c r="D15" s="31"/>
@@ -2130,7 +2130,7 @@
       <c r="G15" s="32"/>
       <c r="H15" s="31"/>
       <c r="I15" s="31" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="J15" s="31"/>
       <c r="K15" s="31"/>
@@ -2178,7 +2178,7 @@
         <v>21</v>
       </c>
       <c r="C17" s="43" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D17" s="44" t="s">
         <v>22</v>
@@ -2208,20 +2208,20 @@
         <v>24</v>
       </c>
       <c r="B18" s="65" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="C18" s="66" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="D18" s="66"/>
       <c r="E18" s="66"/>
       <c r="F18" s="66"/>
       <c r="G18" s="66"/>
       <c r="H18" s="65" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="I18" s="66" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="J18" s="66" t="s">
         <v>13</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="19" spans="1:22" s="28" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A19" s="65" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="B19" s="65" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="C19" s="66"/>
       <c r="D19" s="66"/>
@@ -2248,7 +2248,7 @@
       <c r="G19" s="66"/>
       <c r="H19" s="65"/>
       <c r="I19" s="66" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="J19" s="66"/>
       <c r="K19" s="66"/>
@@ -2259,10 +2259,10 @@
     </row>
     <row r="20" spans="1:22" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="65" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="B20" s="65" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="C20" s="65"/>
       <c r="D20" s="65"/>
@@ -2271,7 +2271,7 @@
       <c r="G20" s="65"/>
       <c r="H20" s="65"/>
       <c r="I20" s="65" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="J20" s="65"/>
       <c r="K20" s="65"/>
@@ -2285,24 +2285,24 @@
         <v>23</v>
       </c>
       <c r="B21" s="47" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="C21" s="43" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="D21" s="43"/>
       <c r="E21" s="42"/>
       <c r="F21" s="46" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="G21" s="44" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="H21" s="47" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="I21" s="47" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="J21" s="42" t="s">
         <v>13</v>
@@ -2320,10 +2320,10 @@
       <c r="S21" s="45"/>
       <c r="T21" s="49"/>
       <c r="U21" s="49" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="V21" s="50" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="22" spans="1:22" s="15" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
@@ -2334,20 +2334,20 @@
         <v>25</v>
       </c>
       <c r="C22" s="43" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="D22" s="43" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="E22" s="45"/>
       <c r="F22" s="46" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="G22" s="43" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H22" s="47" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="I22" s="45"/>
       <c r="J22" s="42" t="s">
@@ -2373,14 +2373,14 @@
         <v>27</v>
       </c>
       <c r="C23" s="43" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="D23" s="44"/>
       <c r="E23" s="45"/>
       <c r="F23" s="45"/>
       <c r="G23" s="51"/>
       <c r="H23" s="47" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="I23" s="45"/>
       <c r="J23" s="42" t="s">
@@ -2400,20 +2400,20 @@
     </row>
     <row r="24" spans="1:22" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="38" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="B24" s="47" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C24" s="43" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="D24" s="44"/>
       <c r="E24" s="45"/>
       <c r="F24" s="45"/>
       <c r="G24" s="51"/>
       <c r="H24" s="47" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="I24" s="45"/>
       <c r="J24" s="42" t="s">
@@ -2436,21 +2436,21 @@
         <v>24</v>
       </c>
       <c r="B25" s="47" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C25" s="43" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="D25" s="44"/>
       <c r="E25" s="45"/>
       <c r="F25" s="45" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="G25" s="51" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="H25" s="47" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="I25" s="45"/>
       <c r="J25" s="42" t="s">
@@ -2493,24 +2493,24 @@
     </row>
     <row r="27" spans="1:22" s="15" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A27" s="38" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="B27" s="47" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C27" s="43" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="D27" s="44"/>
       <c r="E27" s="45"/>
       <c r="F27" s="45" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="G27" s="51" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="H27" s="47" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="I27" s="45"/>
       <c r="J27" s="47" t="s">
@@ -2530,20 +2530,20 @@
     </row>
     <row r="28" spans="1:22" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="38" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B28" s="47" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C28" s="43" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="D28" s="44"/>
       <c r="E28" s="45"/>
       <c r="F28" s="45"/>
       <c r="G28" s="51"/>
       <c r="H28" s="47" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="I28" s="45"/>
       <c r="J28" s="47" t="s">
@@ -2563,20 +2563,20 @@
     </row>
     <row r="29" spans="1:22" s="15" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A29" s="38" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="B29" s="47" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C29" s="43" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="D29" s="44"/>
       <c r="E29" s="45"/>
       <c r="F29" s="45"/>
       <c r="G29" s="51"/>
       <c r="H29" s="47" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="I29" s="45"/>
       <c r="J29" s="47" t="s">
@@ -2596,20 +2596,20 @@
     </row>
     <row r="30" spans="1:22" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="38" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B30" s="47" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C30" s="43" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="D30" s="44"/>
       <c r="E30" s="45"/>
       <c r="F30" s="45"/>
       <c r="G30" s="51"/>
       <c r="H30" s="47" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="I30" s="45"/>
       <c r="J30" s="47" t="s">
@@ -2629,20 +2629,20 @@
     </row>
     <row r="31" spans="1:22" s="15" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A31" s="38" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B31" s="47" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C31" s="43" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="D31" s="44"/>
       <c r="E31" s="45"/>
       <c r="F31" s="45"/>
       <c r="G31" s="51"/>
       <c r="H31" s="47" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="I31" s="45"/>
       <c r="J31" s="47" t="s">
@@ -2662,20 +2662,20 @@
     </row>
     <row r="32" spans="1:22" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="38" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B32" s="47" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="C32" s="43" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="D32" s="44"/>
       <c r="E32" s="45"/>
       <c r="F32" s="45"/>
       <c r="G32" s="51"/>
       <c r="H32" s="47" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="I32" s="45"/>
       <c r="J32" s="47" t="s">
@@ -2695,20 +2695,20 @@
     </row>
     <row r="33" spans="1:21" s="15" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A33" s="38" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="B33" s="47" t="s">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="C33" s="43" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="D33" s="44"/>
       <c r="E33" s="45"/>
       <c r="F33" s="45"/>
       <c r="G33" s="51"/>
       <c r="H33" s="47" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="I33" s="45"/>
       <c r="J33" s="47" t="s">
@@ -2728,20 +2728,20 @@
     </row>
     <row r="34" spans="1:21" s="15" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A34" s="38" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="B34" s="47" t="s">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="C34" s="43" t="s">
-        <v>281</v>
+        <v>267</v>
       </c>
       <c r="D34" s="44"/>
       <c r="E34" s="45"/>
       <c r="F34" s="45"/>
       <c r="G34" s="51"/>
       <c r="H34" s="47" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="I34" s="45"/>
       <c r="J34" s="47" t="s">
@@ -2767,14 +2767,14 @@
         <v>28</v>
       </c>
       <c r="C35" s="54" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="D35" s="55"/>
       <c r="E35" s="56"/>
       <c r="F35" s="56"/>
       <c r="G35" s="55"/>
       <c r="H35" s="46" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="I35" s="56"/>
       <c r="J35" s="56"/>
@@ -2798,7 +2798,7 @@
         <v>29</v>
       </c>
       <c r="C36" s="54" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="D36" s="55"/>
       <c r="E36" s="56"/>
@@ -2824,17 +2824,17 @@
         <v>18</v>
       </c>
       <c r="B37" s="53" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C37" s="54" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D37" s="55"/>
       <c r="E37" s="56"/>
       <c r="F37" s="56"/>
       <c r="G37" s="55"/>
       <c r="H37" s="47" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="I37" s="56"/>
       <c r="J37" s="56"/>
@@ -2875,7 +2875,7 @@
     </row>
     <row r="39" spans="1:21" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="52" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="B39" s="57"/>
       <c r="C39" s="58"/>
@@ -2900,10 +2900,10 @@
     </row>
     <row r="40" spans="1:21" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="65" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="B40" s="66" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="C40" s="66"/>
       <c r="D40" s="66"/>
@@ -2912,7 +2912,7 @@
       <c r="G40" s="65"/>
       <c r="H40" s="47"/>
       <c r="I40" s="65" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="J40" s="65"/>
       <c r="K40" s="65"/>
@@ -3004,7 +3004,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="E1" s="20" t="s">
         <v>35</v>
@@ -3013,7 +3013,7 @@
         <v>36</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -3087,7 +3087,7 @@
         <v>43</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>44</v>
@@ -3099,7 +3099,7 @@
         <v>43</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>45</v>
@@ -3120,7 +3120,7 @@
         <v>47</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>48</v>
+        <v>277</v>
       </c>
       <c r="D12" s="21"/>
     </row>
@@ -3129,10 +3129,10 @@
         <v>46</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>50</v>
+        <v>278</v>
       </c>
       <c r="D13" s="21"/>
     </row>
@@ -3141,10 +3141,10 @@
         <v>46</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>52</v>
+        <v>279</v>
       </c>
       <c r="D14" s="21"/>
     </row>
@@ -3153,10 +3153,10 @@
         <v>46</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>54</v>
+        <v>280</v>
       </c>
       <c r="D15" s="21"/>
     </row>
@@ -3165,10 +3165,10 @@
         <v>46</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D16" s="21"/>
     </row>
@@ -3177,10 +3177,10 @@
         <v>46</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D17" s="21"/>
     </row>
@@ -3192,31 +3192,31 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D19" s="21"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="9" t="s">
         <v>58</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>62</v>
       </c>
       <c r="D20" s="21"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>39</v>
@@ -3234,612 +3234,612 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>65</v>
+        <v>281</v>
       </c>
       <c r="D23" s="21"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>67</v>
+        <v>282</v>
       </c>
       <c r="D24" s="21"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" s="9" t="s">
         <v>63</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>69</v>
       </c>
       <c r="D25" s="21"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D26" s="21"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D27" s="21"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D28" s="21"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="B29" s="8" t="s">
-        <v>76</v>
-      </c>
       <c r="C29" s="9" t="s">
-        <v>77</v>
+        <v>283</v>
       </c>
       <c r="D29" s="21"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>79</v>
+        <v>284</v>
       </c>
       <c r="D30" s="21"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D31" s="21"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D32" s="21"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="13" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B38" s="18" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D38" s="18"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>79</v>
+      </c>
+      <c r="B39" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="B39" s="18" t="s">
-        <v>95</v>
-      </c>
       <c r="C39" s="18" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D39" s="18"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C40" s="18" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D40" s="18"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="B42" s="25" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="B43" s="25" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C43" s="25" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="B44" s="25" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C44" s="25" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B46" s="25" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="C46" s="25" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B47" s="25" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B48" s="25" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B49" s="25" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C49" s="25" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="C51" s="17" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="D51" s="10"/>
     </row>
     <row r="52" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="D52" s="10"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="D53" s="10"/>
     </row>
     <row r="54" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="D54" s="10"/>
     </row>
     <row r="55" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C55" s="17" t="s">
-        <v>137</v>
+        <v>285</v>
       </c>
       <c r="D55" s="10"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="D57" s="10"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="D58" s="10"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="B59" s="19" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="C59" s="17" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="D59" s="10"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="8" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="C60" s="17" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="D60" s="10"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="C62" s="17" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="D62" s="10"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="B63" s="19" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="C63" s="17" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="D63" s="10"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="C64" s="17" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="D64" s="10"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="B65" s="19" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C65" s="17" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="D65" s="10"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="B66" s="19" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="C66" s="17" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="D66" s="10"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>159</v>
+        <v>286</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="26" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>77</v>
+        <v>283</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>79</v>
+        <v>284</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="B80" s="25" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C80" s="25" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="B81" s="25" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="C81" s="25" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="B82" s="25" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C82" s="25" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -3848,68 +3848,68 @@
     </row>
     <row r="84" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="B84" s="25" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="C84" s="25" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="B85" s="25" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="C85" s="25" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="B86" s="25" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="C86" s="25" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="B87" s="25" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="C87" s="25" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="B88" s="25" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="C88" s="25" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="B89" s="25" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="C89" s="25" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -3918,46 +3918,46 @@
     </row>
     <row r="91" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A91" s="26" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="B91" s="25" t="s">
-        <v>286</v>
+        <v>272</v>
       </c>
       <c r="C91" s="25" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="26" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="B92" s="25" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="C92" s="25" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A93" s="26" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="B93" s="25" t="s">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="C93" s="25" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="26" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="B94" s="25" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="C94" s="25" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
@@ -3966,51 +3966,51 @@
     </row>
     <row r="96" spans="1:5" s="62" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="59" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="B96" s="59" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="C96" s="60" t="s">
-        <v>227</v>
+        <v>287</v>
       </c>
       <c r="D96" s="59"/>
       <c r="E96" s="61"/>
     </row>
     <row r="97" spans="1:6" s="62" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="59" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="B97" s="59" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C97" s="60" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="D97" s="59"/>
       <c r="E97" s="61"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="B99" s="62" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="C99" t="s">
-        <v>243</v>
+        <v>288</v>
       </c>
       <c r="D99"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="68" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="B101" s="42" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="C101" s="42" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D101" s="42"/>
       <c r="E101" s="42"/>
@@ -4018,13 +4018,13 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="68" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="B102" s="42" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="C102" s="42" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D102" s="42"/>
       <c r="E102" s="42"/>
@@ -4047,24 +4047,24 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/SCH-STH/Impact assessments/Senegal/2025/november/sn_sppa_impact_2511_2_child.xlsx
+++ b/SCH-STH/Impact assessments/Senegal/2025/november/sn_sppa_impact_2511_2_child.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\SCH-STH\Impact assessments\Senegal\2025\november\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A22DF89-8611-422D-904A-839C0D236083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9CFCD35-6A0D-4C4B-A419-C723015D7307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="292">
   <si>
     <t>type</t>
   </si>
@@ -760,18 +760,6 @@
   </si>
   <si>
     <t>Si "Ne fréquente pas" est sélectionné, aucune autre option ne doit l’être.</t>
-  </si>
-  <si>
-    <t>sn_sppa_impact_2511_2_child</t>
-  </si>
-  <si>
-    <t>(2025 Nov) - 2. SCH/STH – Participant</t>
-  </si>
-  <si>
-    <t>p_sppa2511</t>
-  </si>
-  <si>
-    <t>${p_index_init} + indexed-repeat(${position}, ${p_sppa2511}, count(${p_sppa2511}))</t>
   </si>
   <si>
     <r>
@@ -922,6 +910,21 @@
   </si>
   <si>
     <t>En buvant de l.eau sale ou en mangeant des aliments sales.</t>
+  </si>
+  <si>
+    <t>${p_connait_geohelm} = 'Oui'</t>
+  </si>
+  <si>
+    <t>sn_sppa_impact_2511_2_child_v2</t>
+  </si>
+  <si>
+    <t>(2025 Nov) - 2. SCH/STH – Participant V2</t>
+  </si>
+  <si>
+    <t>p_sppa2511_2</t>
+  </si>
+  <si>
+    <t>${p_index_init} + indexed-repeat(${position}, ${p_sppa2511_2}, count(${p_sppa2511_2}))</t>
   </si>
 </sst>
 </file>
@@ -2061,7 +2064,7 @@
         <v>174</v>
       </c>
       <c r="B13" s="48" t="s">
-        <v>246</v>
+        <v>290</v>
       </c>
       <c r="C13" s="48" t="s">
         <v>175</v>
@@ -2334,17 +2337,17 @@
         <v>25</v>
       </c>
       <c r="C22" s="43" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D22" s="43" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="E22" s="45"/>
       <c r="F22" s="46" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="G22" s="43" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H22" s="47" t="s">
         <v>154</v>
@@ -2665,10 +2668,10 @@
         <v>167</v>
       </c>
       <c r="B32" s="47" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C32" s="43" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="D32" s="44"/>
       <c r="E32" s="45"/>
@@ -2695,20 +2698,20 @@
     </row>
     <row r="33" spans="1:21" s="15" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A33" s="38" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B33" s="47" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C33" s="43" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="D33" s="44"/>
       <c r="E33" s="45"/>
       <c r="F33" s="45"/>
       <c r="G33" s="51"/>
       <c r="H33" s="47" t="s">
-        <v>154</v>
+        <v>287</v>
       </c>
       <c r="I33" s="45"/>
       <c r="J33" s="47" t="s">
@@ -2728,20 +2731,20 @@
     </row>
     <row r="34" spans="1:21" s="15" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A34" s="38" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B34" s="47" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C34" s="43" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D34" s="44"/>
       <c r="E34" s="45"/>
       <c r="F34" s="45"/>
       <c r="G34" s="51"/>
       <c r="H34" s="47" t="s">
-        <v>154</v>
+        <v>287</v>
       </c>
       <c r="I34" s="45"/>
       <c r="J34" s="47" t="s">
@@ -2912,7 +2915,7 @@
       <c r="G40" s="65"/>
       <c r="H40" s="47"/>
       <c r="I40" s="65" t="s">
-        <v>247</v>
+        <v>291</v>
       </c>
       <c r="J40" s="65"/>
       <c r="K40" s="65"/>
@@ -3120,7 +3123,7 @@
         <v>47</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="D12" s="21"/>
     </row>
@@ -3132,7 +3135,7 @@
         <v>48</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="D13" s="21"/>
     </row>
@@ -3144,7 +3147,7 @@
         <v>49</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="D14" s="21"/>
     </row>
@@ -3156,7 +3159,7 @@
         <v>50</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D15" s="21"/>
     </row>
@@ -3240,7 +3243,7 @@
         <v>60</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="D23" s="21"/>
     </row>
@@ -3252,7 +3255,7 @@
         <v>61</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="D24" s="21"/>
     </row>
@@ -3312,7 +3315,7 @@
         <v>70</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D29" s="21"/>
     </row>
@@ -3324,7 +3327,7 @@
         <v>71</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="D30" s="21"/>
     </row>
@@ -3576,7 +3579,7 @@
         <v>128</v>
       </c>
       <c r="C55" s="17" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D55" s="10"/>
     </row>
@@ -3696,7 +3699,7 @@
         <v>143</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -3773,7 +3776,7 @@
         <v>162</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -3784,7 +3787,7 @@
         <v>71</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -3848,68 +3851,68 @@
     </row>
     <row r="84" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B84" s="25" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C84" s="25" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B85" s="25" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C85" s="25" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B86" s="25" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C86" s="25" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B87" s="25" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="C87" s="25" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B88" s="25" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C88" s="25" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B89" s="25" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C89" s="25" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -3918,46 +3921,46 @@
     </row>
     <row r="91" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A91" s="26" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B91" s="25" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C91" s="25" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="26" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B92" s="25" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C92" s="25" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A93" s="26" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B93" s="25" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C93" s="25" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="26" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B94" s="25" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C94" s="25" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
@@ -3972,7 +3975,7 @@
         <v>215</v>
       </c>
       <c r="C96" s="60" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D96" s="59"/>
       <c r="E96" s="61"/>
@@ -3998,7 +4001,7 @@
         <v>231</v>
       </c>
       <c r="C99" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D99"/>
     </row>
@@ -4058,10 +4061,10 @@
     </row>
     <row r="2" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>245</v>
+        <v>289</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>244</v>
+        <v>288</v>
       </c>
       <c r="C2" t="s">
         <v>92</v>
